--- a/forms/trg/Formulir_TRG_ocnrg.xlsx
+++ b/forms/trg/Formulir_TRG_ocnrg.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B29)</f>
+        <f>COUNTA(Anggota!B5:B30)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F29)</f>
+        <f>COUNTA(Anggota!F5:F30)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M29"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,22 +913,22 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. M. Thahir Haning, M.Si</t>
+          <t>Andi Imam Arundhana Thahir, S.Gz, MPH, Ph.D</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Leader</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
-          <t>Public policy and development administration</t>
+          <t>Department of Nutrition Science, Faculty of Public Health</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Department of Administration Science, Faculty of Social and Political Science</t>
+          <t>Obesity prevention, child health, and gut microbiome</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
@@ -937,17 +937,17 @@
       <c r="I5" s="12" t="n"/>
       <c r="J5" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-7751-454X</t>
+          <t>0000-0002-9926-6604</t>
         </is>
       </c>
       <c r="K5" s="11" t="inlineStr">
         <is>
-          <t>5984489</t>
+          <t>5974577</t>
         </is>
       </c>
       <c r="L5" s="11" t="inlineStr">
         <is>
-          <t>57192678109</t>
+          <t>57189491378</t>
         </is>
       </c>
       <c r="M5" s="11" t="inlineStr">
@@ -962,22 +962,22 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Rahayu Indriasari, SKM, MPHCN, Ph.D</t>
+          <t>Prof. Dr. M. Thahir Haning, M.Si</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>Public health nutrition, nutrition education, and adolescent nutrition</t>
+          <t>Public policy and development administration</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Department of Nutrition Science, Faculty of Public Health</t>
+          <t>Department of Administration Science, Faculty of Social and Political Science</t>
         </is>
       </c>
       <c r="F6" s="12" t="n"/>
@@ -986,17 +986,17 @@
       <c r="I6" s="12" t="n"/>
       <c r="J6" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-0348-2338</t>
+          <t>0000-0002-7751-454X</t>
         </is>
       </c>
       <c r="K6" s="11" t="inlineStr">
         <is>
-          <t>6012699</t>
+          <t>5984489</t>
         </is>
       </c>
       <c r="L6" s="11" t="inlineStr">
         <is>
-          <t>57203151676</t>
+          <t>57192678109</t>
         </is>
       </c>
       <c r="M6" s="11" t="inlineStr">
@@ -1011,22 +1011,22 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Muhammad Rachmat, SKM., M.Kes</t>
+          <t>Rahayu Indriasari, SKM, MPHCN, Ph.D</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>Health promotion and education, media development</t>
+          <t>Public health nutrition, nutrition education, and adolescent nutrition</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Department of Health Promotion and Behavioral Science</t>
+          <t>Department of Nutrition Science, Faculty of Public Health</t>
         </is>
       </c>
       <c r="F7" s="12" t="n"/>
@@ -1035,17 +1035,17 @@
       <c r="I7" s="12" t="n"/>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t>0000-0003-1520-6434</t>
+          <t>0000-0002-0348-2338</t>
         </is>
       </c>
       <c r="K7" s="11" t="inlineStr">
         <is>
-          <t>5979584</t>
+          <t>6012699</t>
         </is>
       </c>
       <c r="L7" s="11" t="inlineStr">
         <is>
-          <t>57208769430</t>
+          <t>57203151676</t>
         </is>
       </c>
       <c r="M7" s="11" t="inlineStr">
@@ -1060,22 +1060,22 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Prof. Mu Li</t>
+          <t>Muhammad Rachmat, SKM., M.Kes</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>Global public health nutrition</t>
+          <t>Health promotion and education, media development</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>School of Public Health, The University of Sydney</t>
+          <t>Department of Health Promotion and Behavioral Science</t>
         </is>
       </c>
       <c r="F8" s="12" t="n"/>
@@ -1084,13 +1084,17 @@
       <c r="I8" s="12" t="n"/>
       <c r="J8" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-2371-8950</t>
-        </is>
-      </c>
-      <c r="K8" s="12" t="n"/>
+          <t>0000-0003-1520-6434</t>
+        </is>
+      </c>
+      <c r="K8" s="11" t="inlineStr">
+        <is>
+          <t>5979584</t>
+        </is>
+      </c>
       <c r="L8" s="11" t="inlineStr">
         <is>
-          <t>36834123000</t>
+          <t>57208769430</t>
         </is>
       </c>
       <c r="M8" s="11" t="inlineStr">
@@ -1105,22 +1109,22 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Assoc. Prof. Andrew Holmes</t>
+          <t>Prof. Mu Li</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>Microbiology, Gut Microbiome</t>
+          <t>Global public health nutrition</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>The University of Sydney</t>
+          <t>School of Public Health, The University of Sydney</t>
         </is>
       </c>
       <c r="F9" s="12" t="n"/>
@@ -1129,13 +1133,13 @@
       <c r="I9" s="12" t="n"/>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-7406-4387</t>
+          <t>0000-0002-2371-8950</t>
         </is>
       </c>
       <c r="K9" s="12" t="n"/>
       <c r="L9" s="11" t="inlineStr">
         <is>
-          <t>7401686958</t>
+          <t>36834123000</t>
         </is>
       </c>
       <c r="M9" s="11" t="inlineStr">
@@ -1150,22 +1154,22 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Laksmi Trisasmita, S.Gz, MKM</t>
+          <t>Assoc. Prof. Andrew Holmes</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>Community nutrition, childhood nutrition</t>
+          <t>Microbiology, Gut Microbiome</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>Department of Nutrition Science, Faculty of Public Health</t>
+          <t>The University of Sydney</t>
         </is>
       </c>
       <c r="F10" s="12" t="n"/>
@@ -1174,17 +1178,13 @@
       <c r="I10" s="12" t="n"/>
       <c r="J10" s="11" t="inlineStr">
         <is>
-          <t>0000-0003-4102-6162</t>
-        </is>
-      </c>
-      <c r="K10" s="11" t="inlineStr">
-        <is>
-          <t>6768340</t>
-        </is>
-      </c>
+          <t>0000-0002-7406-4387</t>
+        </is>
+      </c>
+      <c r="K10" s="12" t="n"/>
       <c r="L10" s="11" t="inlineStr">
         <is>
-          <t>57217310769</t>
+          <t>7401686958</t>
         </is>
       </c>
       <c r="M10" s="11" t="inlineStr">
@@ -1199,31 +1199,43 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Safitri Baniu</t>
+          <t>Laksmi Trisasmita, S.Gz, MKM</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>Nutrition Education</t>
+          <t>Community nutrition, childhood nutrition</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Department of Nutrition Science</t>
+          <t>Department of Nutrition Science, Faculty of Public Health</t>
         </is>
       </c>
       <c r="F11" s="12" t="n"/>
       <c r="G11" s="12" t="n"/>
       <c r="H11" s="12" t="n"/>
       <c r="I11" s="12" t="n"/>
-      <c r="J11" s="12" t="n"/>
-      <c r="K11" s="12" t="n"/>
-      <c r="L11" s="12" t="n"/>
+      <c r="J11" s="11" t="inlineStr">
+        <is>
+          <t>0000-0003-4102-6162</t>
+        </is>
+      </c>
+      <c r="K11" s="11" t="inlineStr">
+        <is>
+          <t>6768340</t>
+        </is>
+      </c>
+      <c r="L11" s="11" t="inlineStr">
+        <is>
+          <t>57217310769</t>
+        </is>
+      </c>
       <c r="M11" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1236,17 +1248,17 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Rizka Nur Aulia</t>
+          <t>Safitri Baniu</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>Diet quality and gut microbiome</t>
+          <t>Nutrition Education</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
@@ -1273,17 +1285,17 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Fitrah Kusuma Pratiwi</t>
+          <t>Rizka Nur Aulia</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>School feeding program, early adolescence nutrition</t>
+          <t>Diet quality and gut microbiome</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
@@ -1310,17 +1322,17 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Siti Nurul Ishlah Amaliyah</t>
+          <t>Fitrah Kusuma Pratiwi</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>Physical activity and nutrition</t>
+          <t>School feeding program, early adolescence nutrition</t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
@@ -1347,17 +1359,17 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Aprilliani War Nurhayati</t>
+          <t>Siti Nurul Ishlah Amaliyah</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>Nutrition and dietetics</t>
+          <t>Physical activity and nutrition</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
@@ -1384,17 +1396,17 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>Swasti Purnama Sari</t>
+          <t>Aprilliani War Nurhayati</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>Nutrition and metabolic, dietary modification</t>
+          <t>Nutrition and dietetics</t>
         </is>
       </c>
       <c r="E16" s="11" t="inlineStr">
@@ -1406,11 +1418,7 @@
       <c r="G16" s="12" t="n"/>
       <c r="H16" s="12" t="n"/>
       <c r="I16" s="12" t="n"/>
-      <c r="J16" s="11" t="inlineStr">
-        <is>
-          <t>0009-0001-2167-3998</t>
-        </is>
-      </c>
+      <c r="J16" s="12" t="n"/>
       <c r="K16" s="12" t="n"/>
       <c r="L16" s="12" t="n"/>
       <c r="M16" s="11" t="inlineStr">
@@ -1425,17 +1433,17 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>Rizka Pratiwi Ibrahim</t>
+          <t>Swasti Purnama Sari</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>Food labelling and nutrition promotion</t>
+          <t>Nutrition and metabolic, dietary modification</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
@@ -1447,7 +1455,11 @@
       <c r="G17" s="12" t="n"/>
       <c r="H17" s="12" t="n"/>
       <c r="I17" s="12" t="n"/>
-      <c r="J17" s="12" t="n"/>
+      <c r="J17" s="11" t="inlineStr">
+        <is>
+          <t>0009-0001-2167-3998</t>
+        </is>
+      </c>
       <c r="K17" s="12" t="n"/>
       <c r="L17" s="12" t="n"/>
       <c r="M17" s="11" t="inlineStr">
@@ -1460,10 +1472,26 @@
       <c r="A18" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="12" t="n"/>
-      <c r="C18" s="12" t="n"/>
-      <c r="D18" s="12" t="n"/>
-      <c r="E18" s="11" t="n"/>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>Rizka Pratiwi Ibrahim</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="inlineStr">
+        <is>
+          <t>Department of Nutrition Science</t>
+        </is>
+      </c>
+      <c r="E18" s="11" t="inlineStr">
+        <is>
+          <t>The Obesity and Child Nutrition Research Group (OC-Nutrition RG) conducts interdisciplinary research to advance understanding of childhood obesity and nutritional health. Guided by the I-GROW RIGHT strategy, the group integrates biological, behavioral, and environmental perspectives to study determinants of child growth and nutrition. Through research, intervention development, and implementation studies in early childhood and school settings, the group aims to generate evidence-based strategies that support effective prevention and improved nutritional outcomes for children.</t>
+        </is>
+      </c>
       <c r="F18" s="12" t="n"/>
       <c r="G18" s="12" t="n"/>
       <c r="H18" s="12" t="n"/>
@@ -1471,7 +1499,11 @@
       <c r="J18" s="12" t="n"/>
       <c r="K18" s="12" t="n"/>
       <c r="L18" s="12" t="n"/>
-      <c r="M18" s="12" t="n"/>
+      <c r="M18" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
@@ -1660,15 +1692,32 @@
       <c r="L29" s="12" t="n"/>
       <c r="M29" s="12" t="n"/>
     </row>
+    <row r="30">
+      <c r="A30" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="12" t="n"/>
+      <c r="C30" s="12" t="n"/>
+      <c r="D30" s="12" t="n"/>
+      <c r="E30" s="11" t="n"/>
+      <c r="F30" s="12" t="n"/>
+      <c r="G30" s="12" t="n"/>
+      <c r="H30" s="12" t="n"/>
+      <c r="I30" s="12" t="n"/>
+      <c r="J30" s="12" t="n"/>
+      <c r="K30" s="12" t="n"/>
+      <c r="L30" s="12" t="n"/>
+      <c r="M30" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
